--- a/docs/downloads/28082026Tduh Developer Project Sales Status 13.xlsx
+++ b/docs/downloads/28082026Tduh Developer Project Sales Status 13.xlsx
@@ -1000,7 +1000,7 @@
         <v/>
       </c>
       <c r="BE5" s="11" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="BF5" s="12">
         <f>BE5/$E$5</f>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="BE6" s="11" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="BF6" s="12">
         <f>BE6/$E$6</f>
@@ -1435,7 +1435,7 @@
         <v/>
       </c>
       <c r="BE7" s="11" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BF7" s="12">
         <f>BE7/$E$7</f>
@@ -2088,7 +2088,7 @@
         <v/>
       </c>
       <c r="BE10" s="11" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="BF10" s="12">
         <f>BE10/$E$10</f>
@@ -2740,7 +2740,7 @@
         <v/>
       </c>
       <c r="BE13" s="11" t="n">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="BF13" s="12">
         <f>BE13/$E$13</f>
@@ -2957,7 +2957,7 @@
         <v/>
       </c>
       <c r="BE14" s="11" t="n">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="BF14" s="12">
         <f>BE14/$E$14</f>
@@ -3174,7 +3174,7 @@
         <v/>
       </c>
       <c r="BE15" s="11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BF15" s="12">
         <f>BE15/$E$15</f>
@@ -3496,7 +3496,7 @@
         <v/>
       </c>
       <c r="BE18" s="11" t="n">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="BF18" s="12">
         <f>BE18/$E$18</f>
